--- a/sample/questionnaire/customer-esg-questionnaire-2026.xlsx
+++ b/sample/questionnaire/customer-esg-questionnaire-2026.xlsx
@@ -413,11 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Report total annual electricity consumption in kWh for the reporting period.</t>
+          <t>SEDG-E1.1: Report total Scope 1 (direct) GHG emissions in metric tonnes of CO2 equivalent for the reporting period.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disclose Scope 1 and Scope 2 greenhouse gas emissions, stating the grid emission factor used.</t>
+          <t>SEDG-E1.2: Report total Scope 2 (indirect) GHG emissions in metric tonnes of CO2 equivalent, stating the grid emission factor used and its source.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>State total water withdrawal by source for the reporting period.</t>
+          <t>SEDG-E1.7: Report total Scope 1 and 2 GHG emissions intensity in metric tonnes of CO2 equivalent per unit of production.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="D4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What percentage of waste generated was recycled or diverted from disposal?</t>
+          <t>SEDG-E2.1: Report total energy consumption in kWh, broken down into electricity purchased from the grid, renewable fuel sources and non-renewable fuel sources.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Describe the environmental policy and state when it was last approved.</t>
+          <t>SEDG-E2.2: Report the reduction in energy consumption achieved as a direct result of conservation and efficiency initiatives, in kWh.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="D6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Does the company purchase or generate renewable energy such as solar?</t>
+          <t>SEDG-E3.1: Report the total water withdrawal from all areas for the reporting period, with a breakdown by source.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -561,23 +561,23 @@
         </is>
       </c>
       <c r="D7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q-S-01</t>
+          <t>Q-E-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Report the work-related injury rate (LTIFR) and any fatalities.</t>
+          <t>SEDG-E4.1: Report total waste generated, total waste diverted from disposal and total waste directed to disposal, in metric tonnes.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -587,17 +587,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q-S-02</t>
+          <t>Q-E-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>State total workforce headcount and the employment type breakdown.</t>
+          <t>SEDG-E4.2: Report total hazardous waste and scheduled waste generated in metric tonnes, identified by waste code.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -607,32 +607,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Q-S-03</t>
+          <t>Q-E-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Report gender diversity, including women in management positions.</t>
+          <t>SEDG-E5.2: Report the percentage of recycled input materials used to manufacture the company's primary products.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="D10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q-S-04</t>
+          <t>Q-S-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>State the average training hours per employee.</t>
+          <t>SEDG-S1.1: Report the number and nature of child labour and forced labour incidents recorded during the reporting period, if any.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -641,18 +641,18 @@
         </is>
       </c>
       <c r="D11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q-S-05</t>
+          <t>Q-S-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Describe the grievance mechanism available to workers.</t>
+          <t>SEDG-S2.1: Report the average hours of training per employee for the reporting period.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -661,23 +661,23 @@
         </is>
       </c>
       <c r="D12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Q-G-01</t>
+          <t>Q-S-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Describe anti-bribery and anti-corruption controls.</t>
+          <t>SEDG-S2.2: Report the total number of employees and the employee turnover rate for the reporting period.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -687,17 +687,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q-G-02</t>
+          <t>Q-S-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Is there a whistleblowing policy, and how many reports were received?</t>
+          <t>SEDG-S3.1: Report the percentage of employees by gender and by age band, including gender diversity in management positions.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -707,41 +707,141 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Q-G-03</t>
+          <t>Q-S-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Describe cybersecurity governance and disclose any data breach in the period.</t>
+          <t>SEDG-S4.1: Report the number of work-related fatalities and the number of work-related injuries, stating the LTIFR and the hours worked it is based on.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="D15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q-G-04</t>
+          <t>Q-S-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Confirm the supplier code of conduct prohibits child labour and forced labour.</t>
+          <t>SEDG-S4.2: Report the total number and percentage of employees trained on health and safety standards during the reporting period.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Q-G-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SEDG-G2.1: List the company's policy commitments, including the code of conduct, the anti-corruption policy and the whistleblowing policy, giving the approval date and the version in force.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="D16" t="b">
-        <v>1</v>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q-G-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SEDG-G4.2: Report the total number and percentage of employees who received training on the company's anti-bribery and anti-corruption policy.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q-G-03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SEDG-G5.1: Report the number and nature of substantiated complaints concerning breaches of customer privacy or loss of customer data, if any.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q-E-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SEDG-E5.1: List the materials and total weights used to package the company's primary products, in metric tonnes.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Environmental</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q-S-07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SEDG-S5.1: Report the total amount of community investments and donations made during the reporting period.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
